--- a/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-mvtec_cable_tiny.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-mvtec_cable_tiny.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="padim" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stfpm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="uflow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,105 +478,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -589,116 +580,107 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>12.44397306442261</v>
+        <v>12.60318684577942</v>
       </c>
       <c r="D2" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0359377861022949</v>
+        <v>0.1882726848125457</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7853881120681763</v>
+        <v>0.7878788113594055</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7725321650505066</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.375043660402298</v>
+        <v>0.3008033633232116</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0697440132498741</v>
+        <v>0.0157599274317423</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0561375953257083</v>
+        <v>0.0549695788489447</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0168881866667005</v>
+        <v>0.04118699921502</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0789476166831122</v>
+        <v>7.091967344284058</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0646079821056789</v>
+        <v>24.73631048202514</v>
       </c>
       <c r="O2" t="n">
-        <v>7.599684000015259</v>
-      </c>
-      <c r="P2" t="n">
-        <v>35.52642750740051</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>29.07359194755555</v>
+        <v>18.53414964675904</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250714-160357</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-152117</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_cable_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>mvtec_cable_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -710,116 +692,107 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>12.46880197525024</v>
+        <v>12.58323645591736</v>
       </c>
       <c r="D3" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0330457687377929</v>
+        <v>0.197448119521141</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8035714030265808</v>
+        <v>0.7876105904579163</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7931034564971924</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3772907257080078</v>
+        <v>0.3016390204429626</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0686578825116157</v>
+        <v>0.0154027297761705</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0560863129794597</v>
+        <v>0.0540175305472479</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0171238994598388</v>
+        <v>0.041107604238722</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0772099574406941</v>
+        <v>6.931228399276733</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06442137771182591</v>
+        <v>24.3078887462616</v>
       </c>
       <c r="O3" t="n">
-        <v>7.70575475692749</v>
-      </c>
-      <c r="P3" t="n">
-        <v>34.74448084831238</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>28.98961997032165</v>
+        <v>18.49842190742493</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250714-160617</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-152325</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_cable_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>mvtec_cable_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -831,116 +804,107 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>12.61470937728882</v>
+        <v>12.63875985145569</v>
       </c>
       <c r="D4" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0347397327423095</v>
+        <v>0.1942667663097381</v>
       </c>
       <c r="F4" t="n">
-        <v>0.792792797088623</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.782608687877655</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3724340498447418</v>
+        <v>0.2969194948673248</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0689462348818779</v>
+        <v>0.0153390884399414</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0565960891544818</v>
+        <v>0.0542660607231987</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0166135496563381</v>
+        <v>0.0414899746576945</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0775933541191948</v>
+        <v>6.902589797973633</v>
       </c>
       <c r="N4" t="n">
-        <v>0.064795831574334</v>
+        <v>24.41972732543945</v>
       </c>
       <c r="O4" t="n">
-        <v>7.476097345352173</v>
-      </c>
-      <c r="P4" t="n">
-        <v>34.9170093536377</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>29.15812420845032</v>
+        <v>18.67048859596252</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250714-160837</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-152530</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_cable_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>mvtec_cable_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -952,116 +916,107 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>12.46509194374084</v>
+        <v>12.74998331069946</v>
       </c>
       <c r="D5" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0337743759155273</v>
+        <v>0.1866318881511688</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7943925261497498</v>
+        <v>0.7963801026344299</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7929515242576599</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3671241402626037</v>
+        <v>0.2971888184547424</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0693130269646644</v>
+        <v>0.0154315217336018</v>
       </c>
       <c r="K5" t="n">
-        <v>0.054926261305809</v>
+        <v>0.053991003036499</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0166575643751356</v>
+        <v>0.0408697006437513</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0780686929490831</v>
+        <v>6.94418478012085</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0631879848904079</v>
+        <v>24.29595136642456</v>
       </c>
       <c r="O5" t="n">
-        <v>7.495903968811035</v>
-      </c>
-      <c r="P5" t="n">
-        <v>35.1309118270874</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>28.4345932006836</v>
+        <v>18.39136528968811</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250714-161056</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-152737</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_cable_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>mvtec_cable_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1073,116 +1028,107 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>12.66295313835144</v>
+        <v>12.9245457649231</v>
       </c>
       <c r="D6" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0332851409912109</v>
+        <v>0.1867476850748062</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7945205569267273</v>
+        <v>0.7982062697410583</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7763713002204895</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.373203843832016</v>
+        <v>0.300541877746582</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0683261156082153</v>
+        <v>0.0154102738698323</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0570103116333484</v>
+        <v>0.0541336891386244</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0165389823913574</v>
+        <v>0.0410370646582709</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0770998356077406</v>
+        <v>6.934623241424561</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0649514293670654</v>
+        <v>24.36016011238098</v>
       </c>
       <c r="O6" t="n">
-        <v>7.44254207611084</v>
-      </c>
-      <c r="P6" t="n">
-        <v>34.69492602348328</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>29.22814321517944</v>
+        <v>18.46667909622192</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250714-161315</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-152942</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_cable_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>mvtec_cable_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,105 +1194,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -1357,119 +1293,110 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>40.30312418937683</v>
+        <v>588.5453488826752</v>
       </c>
       <c r="D2" t="n">
-        <v>1.769999980926514</v>
+        <v>1.659999966621399</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0186531543731689</v>
+        <v>0.02373814816502</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7551867365837097</v>
+        <v>0.8426395654678345</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7603305578231812</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7155172228813171</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4100642502307892</v>
+        <v>0.291437417268753</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0618267431855201</v>
+        <v>0.0150985627704196</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0512540191411972</v>
+        <v>0.0449409516652425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0183826043870713</v>
+        <v>0.0346894900004069</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07138604376051159</v>
+        <v>6.794353246688843</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0604523266686333</v>
+        <v>20.22342824935913</v>
       </c>
       <c r="O2" t="n">
-        <v>8.272171974182129</v>
-      </c>
-      <c r="P2" t="n">
-        <v>32.12371969223022</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>27.20354700088501</v>
+        <v>15.6102705001831</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250715-220259</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-163818</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_cable_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>mvtec_cable_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1478,119 +1405,110 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="C3" t="n">
-        <v>41.75750136375427</v>
+        <v>587.8981800079346</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75</v>
+        <v>1.740000009536743</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0202906131744384</v>
+        <v>0.0237697607414288</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7551867365837097</v>
+        <v>0.8260869383811951</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7603305578231812</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3529427647590637</v>
+        <v>0.2891561686992645</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0619963370263576</v>
+        <v>0.0153111230002509</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0499017126858234</v>
+        <v>0.0465856488545735</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0163578711615668</v>
+        <v>0.0358601098590427</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0714371506373087</v>
+        <v>6.890005350112915</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0590957599216037</v>
+        <v>20.96354198455811</v>
       </c>
       <c r="O3" t="n">
-        <v>7.361042022705078</v>
-      </c>
-      <c r="P3" t="n">
-        <v>32.14671778678894</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>26.59309196472168</v>
+        <v>16.13704943656921</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250715-22</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-164047</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_cable_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>mvtec_cable_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1599,119 +1517,110 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>45.62272596359253</v>
+        <v>642.4049701690674</v>
       </c>
       <c r="D4" t="n">
-        <v>1.75</v>
+        <v>1.759999990463257</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0185788472493488</v>
+        <v>0.023746177996114</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7565217614173889</v>
+        <v>0.8301886916160583</v>
       </c>
       <c r="G4" t="n">
-        <v>0.756302535533905</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6875</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3709223866462707</v>
+        <v>0.2923648357391357</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0620235502719879</v>
+        <v>0.0149219216240776</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0519811064004898</v>
+        <v>0.0453894768820868</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0172433508767022</v>
+        <v>0.0347580999798244</v>
       </c>
       <c r="M4" t="n">
-        <v>0.071681621339586</v>
+        <v>6.714864730834961</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0619528426064385</v>
+        <v>20.42526459693909</v>
       </c>
       <c r="O4" t="n">
-        <v>7.759507894515991</v>
-      </c>
-      <c r="P4" t="n">
-        <v>32.25672960281372</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>27.87877917289734</v>
+        <v>15.64114499092102</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250715-222735</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-164316</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_cable_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>mvtec_cable_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1720,119 +1629,110 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="C5" t="n">
-        <v>39.55102157592773</v>
+        <v>800.0215775966644</v>
       </c>
       <c r="D5" t="n">
-        <v>1.769999980926514</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0162619113922118</v>
+        <v>0.0239088404923677</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7551867365837097</v>
+        <v>0.8333333134651184</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7603305578231812</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7603305578231812</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5317667722702026</v>
+        <v>0.2921344637870788</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0612997859716415</v>
+        <v>0.0150873788197835</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0512839369475841</v>
+        <v>0.0451939397388034</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0220491472880045</v>
+        <v>0.0346359915203518</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07095525264739989</v>
+        <v>6.789320468902588</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0611254109276665</v>
+        <v>20.33727288246155</v>
       </c>
       <c r="O5" t="n">
-        <v>9.922116279602051</v>
-      </c>
-      <c r="P5" t="n">
-        <v>31.92986369132996</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>27.50643491744995</v>
+        <v>15.58619618415832</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250715-224016</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-164552</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_cable_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>mvtec_cable_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1841,119 +1741,826 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="C6" t="n">
-        <v>40.07391428947449</v>
+        <v>589.7112526893616</v>
       </c>
       <c r="D6" t="n">
-        <v>1.75</v>
+        <v>1.659999966621399</v>
       </c>
       <c r="E6" t="n">
-        <v>0.019708490371704</v>
+        <v>0.0237703781574964</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7551867365837097</v>
+        <v>0.8365384340286255</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7603305578231812</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3501179218292236</v>
+        <v>0.290248692035675</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0610666424036026</v>
+        <v>0.014995289908515</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0516453199088573</v>
+        <v>0.0450039895375569</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0163907453748914</v>
+        <v>0.0349425257576836</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0705988380644056</v>
+        <v>6.747880458831787</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0610332451926337</v>
+        <v>20.25179529190063</v>
       </c>
       <c r="O6" t="n">
-        <v>7.375835418701172</v>
-      </c>
-      <c r="P6" t="n">
-        <v>31.76947712898254</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>27.46496033668518</v>
+        <v>15.72413659095764</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250715-225535</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-164823</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>tiny</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>mvtec_cable_tiny</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>training:epoch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>training:e2e_time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>training:gpu_mem</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>training:train/iter_time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/iter_time</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/latency</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/latency</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/latency</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>data_group</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>otx_version</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>otx_ref</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>test_branch</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>test_commit</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>cpu_info</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>accelerator_info</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>machine_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>199</v>
+      </c>
+      <c r="C2" t="n">
+        <v>962.7290008068084</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.159999847412109</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0980071999769114</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7659574747085571</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5759739279747009</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0263530344433254</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.07698119693332239</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0719818835788303</v>
+      </c>
+      <c r="M2" t="n">
+        <v>11.85886549949646</v>
+      </c>
+      <c r="N2" t="n">
+        <v>34.64153861999512</v>
+      </c>
+      <c r="O2" t="n">
+        <v>32.39184761047363</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250714-172527</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>tiny</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>mvtec_cable_tiny</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>199</v>
+      </c>
+      <c r="C3" t="n">
+        <v>961.7952656745912</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.309999942779541</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0979678678003387</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7758620977401733</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4832013249397278</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0229511377546522</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.1200990592108832</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.07419308927324079</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10.32801198959351</v>
+      </c>
+      <c r="N3" t="n">
+        <v>54.04457664489746</v>
+      </c>
+      <c r="O3" t="n">
+        <v>33.38689017295837</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250714-174350</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>tiny</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>mvtec_cable_tiny</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>199</v>
+      </c>
+      <c r="C4" t="n">
+        <v>973.1866745948792</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.159999847412109</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0981699475017024</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7583333253860474</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5106237530708313</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0239007261064317</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0815576447380913</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0727334520551893</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10.75532674789429</v>
+      </c>
+      <c r="N4" t="n">
+        <v>36.70094013214111</v>
+      </c>
+      <c r="O4" t="n">
+        <v>32.73005342483521</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250714-180233</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>tiny</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>mvtec_cable_tiny</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>199</v>
+      </c>
+      <c r="C5" t="n">
+        <v>980.8277597427368</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.300000190734863</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.098654337077584</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7878788113594055</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5464934706687927</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0253173208236694</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.07972744676801891</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0732941643397013</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11.39279437065124</v>
+      </c>
+      <c r="N5" t="n">
+        <v>35.87735104560852</v>
+      </c>
+      <c r="O5" t="n">
+        <v>32.9823739528656</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250714-182108</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>tiny</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>mvtec_cable_tiny</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>199</v>
+      </c>
+      <c r="C6" t="n">
+        <v>984.6784598827362</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.09857414775158289</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7739130258560181</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4635308086872101</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0225175115797254</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0793255270851983</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0731621450848049</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10.13288021087646</v>
+      </c>
+      <c r="N6" t="n">
+        <v>35.69648718833923</v>
+      </c>
+      <c r="O6" t="n">
+        <v>32.92296528816223</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250714-183952</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>tiny</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_cable_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>mvtec_cable_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
